--- a/data/nzd0249/nzd0249.xlsx
+++ b/data/nzd0249/nzd0249.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R441"/>
+  <dimension ref="A1:R442"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26892,6 +26892,66 @@
         <v>324.68</v>
       </c>
       <c r="R441" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-14 21:53:40+00:00</t>
+        </is>
+      </c>
+      <c r="B442" t="n">
+        <v>305.55</v>
+      </c>
+      <c r="C442" t="n">
+        <v>305.92</v>
+      </c>
+      <c r="D442" t="n">
+        <v>313.7</v>
+      </c>
+      <c r="E442" t="n">
+        <v>312.27</v>
+      </c>
+      <c r="F442" t="n">
+        <v>317.26</v>
+      </c>
+      <c r="G442" t="n">
+        <v>323.08</v>
+      </c>
+      <c r="H442" t="n">
+        <v>330.69</v>
+      </c>
+      <c r="I442" t="n">
+        <v>335.82</v>
+      </c>
+      <c r="J442" t="n">
+        <v>334.79</v>
+      </c>
+      <c r="K442" t="n">
+        <v>327.63</v>
+      </c>
+      <c r="L442" t="n">
+        <v>323.06</v>
+      </c>
+      <c r="M442" t="n">
+        <v>324.06</v>
+      </c>
+      <c r="N442" t="n">
+        <v>335.07</v>
+      </c>
+      <c r="O442" t="n">
+        <v>349.68</v>
+      </c>
+      <c r="P442" t="n">
+        <v>337.09</v>
+      </c>
+      <c r="Q442" t="n">
+        <v>320.71</v>
+      </c>
+      <c r="R442" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -26908,7 +26968,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B443"/>
+  <dimension ref="A1:B444"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31341,6 +31401,16 @@
       </c>
       <c r="B443" t="n">
         <v>-0.76</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>2026-07-14 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B444" t="n">
+        <v>-0.33</v>
       </c>
     </row>
   </sheetData>
@@ -31509,28 +31579,28 @@
         <v>0.0823</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.01874796652860891</v>
+        <v>-0.02173484726003266</v>
       </c>
       <c r="J2" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="K2" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002398548760921271</v>
+        <v>0.0003237703801177716</v>
       </c>
       <c r="M2" t="n">
-        <v>7.246516483265987</v>
+        <v>7.243716581890233</v>
       </c>
       <c r="N2" t="n">
-        <v>83.91070100868887</v>
+        <v>83.81163834062525</v>
       </c>
       <c r="O2" t="n">
-        <v>9.160278435107138</v>
+        <v>9.15486965175503</v>
       </c>
       <c r="P2" t="n">
-        <v>312.4414538171218</v>
+        <v>312.4721963638281</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -31587,28 +31657,28 @@
         <v>0.08450000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.05532270612620103</v>
+        <v>0.05193313746134808</v>
       </c>
       <c r="J3" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="K3" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003213211598017462</v>
+        <v>0.002842041948228791</v>
       </c>
       <c r="M3" t="n">
-        <v>5.837016671906574</v>
+        <v>5.8400317979106</v>
       </c>
       <c r="N3" t="n">
-        <v>54.37903804574123</v>
+        <v>54.37402616039387</v>
       </c>
       <c r="O3" t="n">
-        <v>7.374214401937418</v>
+        <v>7.373874569071125</v>
       </c>
       <c r="P3" t="n">
-        <v>311.6791888285757</v>
+        <v>311.714076051188</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -31665,28 +31735,28 @@
         <v>0.059</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2002300404670669</v>
+        <v>0.1991660112257905</v>
       </c>
       <c r="J4" t="n">
+        <v>441</v>
+      </c>
+      <c r="K4" t="n">
         <v>440</v>
       </c>
-      <c r="K4" t="n">
-        <v>439</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.06220936048077097</v>
+        <v>0.06189143636458649</v>
       </c>
       <c r="M4" t="n">
-        <v>4.788848382657804</v>
+        <v>4.783170217530283</v>
       </c>
       <c r="N4" t="n">
-        <v>34.47165202891619</v>
+        <v>34.40498339380943</v>
       </c>
       <c r="O4" t="n">
-        <v>5.871256426772399</v>
+        <v>5.865576134857465</v>
       </c>
       <c r="P4" t="n">
-        <v>310.5836738819607</v>
+        <v>310.5946404728918</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -31743,28 +31813,28 @@
         <v>0.09429999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1307696838508014</v>
+        <v>0.1280888288997807</v>
       </c>
       <c r="J5" t="n">
+        <v>441</v>
+      </c>
+      <c r="K5" t="n">
         <v>440</v>
       </c>
-      <c r="K5" t="n">
-        <v>439</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.01720393060119574</v>
+        <v>0.01658569052462167</v>
       </c>
       <c r="M5" t="n">
-        <v>5.899527740344775</v>
+        <v>5.901207311214059</v>
       </c>
       <c r="N5" t="n">
-        <v>55.71900425087372</v>
+        <v>55.66649002172031</v>
       </c>
       <c r="O5" t="n">
-        <v>7.464516344069033</v>
+        <v>7.460997923985793</v>
       </c>
       <c r="P5" t="n">
-        <v>314.4851023722956</v>
+        <v>314.5127330411277</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31821,28 +31891,28 @@
         <v>0.0727</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1384326373587678</v>
+        <v>0.1349687429051611</v>
       </c>
       <c r="J6" t="n">
+        <v>441</v>
+      </c>
+      <c r="K6" t="n">
         <v>440</v>
       </c>
-      <c r="K6" t="n">
-        <v>439</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.0165940066289173</v>
+        <v>0.01584325512209594</v>
       </c>
       <c r="M6" t="n">
-        <v>5.941909684754099</v>
+        <v>5.9497739379227</v>
       </c>
       <c r="N6" t="n">
-        <v>64.77568995767382</v>
+        <v>64.75221453552786</v>
       </c>
       <c r="O6" t="n">
-        <v>8.048334607710704</v>
+        <v>8.04687607308127</v>
       </c>
       <c r="P6" t="n">
-        <v>320.9357147447357</v>
+        <v>320.9714159379242</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31899,28 +31969,28 @@
         <v>0.0653</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2903262479983024</v>
+        <v>0.2858217192464414</v>
       </c>
       <c r="J7" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="K7" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08543880024077177</v>
+        <v>0.08313584429028131</v>
       </c>
       <c r="M7" t="n">
-        <v>5.41309440292139</v>
+        <v>5.425455003484668</v>
       </c>
       <c r="N7" t="n">
-        <v>51.81366629393477</v>
+        <v>51.90755272013408</v>
       </c>
       <c r="O7" t="n">
-        <v>7.198171038113416</v>
+        <v>7.204689633851973</v>
       </c>
       <c r="P7" t="n">
-        <v>324.9510618437674</v>
+        <v>324.9972483102602</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -31977,28 +32047,28 @@
         <v>0.0597</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2667249005984082</v>
+        <v>0.2623792979190482</v>
       </c>
       <c r="J8" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="K8" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0894357315038129</v>
+        <v>0.08685843444625196</v>
       </c>
       <c r="M8" t="n">
-        <v>5.023671255451468</v>
+        <v>5.034443399477302</v>
       </c>
       <c r="N8" t="n">
-        <v>41.59496410316797</v>
+        <v>41.69736990388904</v>
       </c>
       <c r="O8" t="n">
-        <v>6.449415795494036</v>
+        <v>6.457350068246962</v>
       </c>
       <c r="P8" t="n">
-        <v>332.8574249554239</v>
+        <v>332.9019818988018</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -32055,28 +32125,28 @@
         <v>0.0568</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1647432204395158</v>
+        <v>0.1633183622190714</v>
       </c>
       <c r="J9" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="K9" t="n">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04001004472177561</v>
+        <v>0.03953523791003921</v>
       </c>
       <c r="M9" t="n">
-        <v>4.796914173179482</v>
+        <v>4.794558705311379</v>
       </c>
       <c r="N9" t="n">
-        <v>37.55237995680994</v>
+        <v>37.48810507066019</v>
       </c>
       <c r="O9" t="n">
-        <v>6.127999670105241</v>
+        <v>6.122753063015051</v>
       </c>
       <c r="P9" t="n">
-        <v>334.4516035801022</v>
+        <v>334.4661926854775</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -32133,28 +32203,28 @@
         <v>0.0615</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1425996307086948</v>
+        <v>0.142628331379719</v>
       </c>
       <c r="J10" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="K10" t="n">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02915318773006492</v>
+        <v>0.02932093292180982</v>
       </c>
       <c r="M10" t="n">
-        <v>4.78024229195125</v>
+        <v>4.769485680551765</v>
       </c>
       <c r="N10" t="n">
-        <v>39.05046169692864</v>
+        <v>38.9615171094815</v>
       </c>
       <c r="O10" t="n">
-        <v>6.249036861543436</v>
+        <v>6.241916140856227</v>
       </c>
       <c r="P10" t="n">
-        <v>330.8831828910227</v>
+        <v>330.8828890252136</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32211,28 +32281,28 @@
         <v>0.0587</v>
       </c>
       <c r="I11" t="n">
-        <v>0.04142183520354092</v>
+        <v>0.04381608199642092</v>
       </c>
       <c r="J11" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="K11" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="L11" t="n">
-        <v>0.001830375005511642</v>
+        <v>0.002056656527912759</v>
       </c>
       <c r="M11" t="n">
-        <v>6.064573020360192</v>
+        <v>6.06238587076793</v>
       </c>
       <c r="N11" t="n">
-        <v>53.73249852311392</v>
+        <v>53.67037317177443</v>
       </c>
       <c r="O11" t="n">
-        <v>7.330245461313961</v>
+        <v>7.326006631977235</v>
       </c>
       <c r="P11" t="n">
-        <v>321.3656098418526</v>
+        <v>321.3410608145588</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -32289,28 +32359,28 @@
         <v>0.0634</v>
       </c>
       <c r="I12" t="n">
-        <v>0.06014659228230709</v>
+        <v>0.06284045900597923</v>
       </c>
       <c r="J12" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="K12" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="L12" t="n">
-        <v>0.00310109627560462</v>
+        <v>0.003398950987416938</v>
       </c>
       <c r="M12" t="n">
-        <v>6.685728231311039</v>
+        <v>6.683654225410669</v>
       </c>
       <c r="N12" t="n">
-        <v>66.78393604610972</v>
+        <v>66.70809696968196</v>
       </c>
       <c r="O12" t="n">
-        <v>8.172143907574664</v>
+        <v>8.167502492787007</v>
       </c>
       <c r="P12" t="n">
-        <v>315.6403911377183</v>
+        <v>315.6127700052929</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -32367,28 +32437,28 @@
         <v>0.0605</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.001991689374484729</v>
+        <v>0.001723551453895447</v>
       </c>
       <c r="J13" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="K13" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="L13" t="n">
-        <v>2.426717723436056e-06</v>
+        <v>1.824541773443045e-06</v>
       </c>
       <c r="M13" t="n">
-        <v>7.928066736685431</v>
+        <v>7.92770106239241</v>
       </c>
       <c r="N13" t="n">
-        <v>93.8721978663409</v>
+        <v>93.80312764904191</v>
       </c>
       <c r="O13" t="n">
-        <v>9.688766581270338</v>
+        <v>9.685201476946254</v>
       </c>
       <c r="P13" t="n">
-        <v>316.1157822264009</v>
+        <v>316.0776885976365</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -32445,28 +32515,28 @@
         <v>0.0692</v>
       </c>
       <c r="I14" t="n">
-        <v>0.06556644095631271</v>
+        <v>0.06991237687653848</v>
       </c>
       <c r="J14" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="K14" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="L14" t="n">
-        <v>0.003044770653071072</v>
+        <v>0.003470969791316669</v>
       </c>
       <c r="M14" t="n">
-        <v>7.02580671025957</v>
+        <v>7.031369921065986</v>
       </c>
       <c r="N14" t="n">
-        <v>80.83480226248635</v>
+        <v>80.84825901114328</v>
       </c>
       <c r="O14" t="n">
-        <v>8.990817663732612</v>
+        <v>8.991565993259643</v>
       </c>
       <c r="P14" t="n">
-        <v>323.9477336892189</v>
+        <v>323.903173329009</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -32523,28 +32593,28 @@
         <v>0.07530000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1393244848922367</v>
+        <v>0.145066425666182</v>
       </c>
       <c r="J15" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="K15" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="L15" t="n">
-        <v>0.01181837765317884</v>
+        <v>0.01282298879461019</v>
       </c>
       <c r="M15" t="n">
-        <v>7.609040105818534</v>
+        <v>7.619862689911382</v>
       </c>
       <c r="N15" t="n">
-        <v>93.20686282258373</v>
+        <v>93.33897078465949</v>
       </c>
       <c r="O15" t="n">
-        <v>9.654370141163209</v>
+        <v>9.661209592212535</v>
       </c>
       <c r="P15" t="n">
-        <v>333.5713623362155</v>
+        <v>333.5124882630843</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -32601,28 +32671,28 @@
         <v>0.0862</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1495229865827722</v>
+        <v>0.1556914388810349</v>
       </c>
       <c r="J16" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="K16" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="L16" t="n">
-        <v>0.01308384177656641</v>
+        <v>0.01418989303707452</v>
       </c>
       <c r="M16" t="n">
-        <v>7.687448184048474</v>
+        <v>7.699191824815121</v>
       </c>
       <c r="N16" t="n">
-        <v>96.84450671824015</v>
+        <v>97.02128575475605</v>
       </c>
       <c r="O16" t="n">
-        <v>9.840960660333938</v>
+        <v>9.849938362992738</v>
       </c>
       <c r="P16" t="n">
-        <v>319.7934129380188</v>
+        <v>319.7301656970576</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -32679,28 +32749,28 @@
         <v>0.0844</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2293636833890716</v>
+        <v>0.2330854956462788</v>
       </c>
       <c r="J17" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="K17" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="L17" t="n">
-        <v>0.03485904370543946</v>
+        <v>0.03609003786373932</v>
       </c>
       <c r="M17" t="n">
-        <v>7.269942971072354</v>
+        <v>7.27142974931463</v>
       </c>
       <c r="N17" t="n">
-        <v>83.64474755359124</v>
+        <v>83.59937795482071</v>
       </c>
       <c r="O17" t="n">
-        <v>9.145750245528863</v>
+        <v>9.143269544031867</v>
       </c>
       <c r="P17" t="n">
-        <v>306.5242784987929</v>
+        <v>306.4861174909319</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -32738,7 +32808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R441"/>
+  <dimension ref="A1:R442"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73261,6 +73331,98 @@
         </is>
       </c>
     </row>
+    <row r="442">
+      <c r="A442" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-14 21:53:40+00:00</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>-38.20573716119925,178.33372277836685</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>-38.20644241063524,178.33375725716502</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>-38.20714289814269,178.33387593116888</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>-38.20784928892946,178.33388995848549</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>-38.20855155297515,178.3339769332658</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>-38.209235228304685,178.33407367609166</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>-38.20992343139393,178.33408732915754</t>
+        </is>
+      </c>
+      <c r="I442" t="inlineStr">
+        <is>
+          <t>-38.21062867373945,178.33406934720608</t>
+        </is>
+      </c>
+      <c r="J442" t="inlineStr">
+        <is>
+          <t>-38.21133152011582,178.33398123396688</t>
+        </is>
+      </c>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>-38.21202472490392,178.3338245302799</t>
+        </is>
+      </c>
+      <c r="L442" t="inlineStr">
+        <is>
+          <t>-38.21269578678568,178.33365437120017</t>
+        </is>
+      </c>
+      <c r="M442" t="inlineStr">
+        <is>
+          <t>-38.213368733531354,178.33345889367794</t>
+        </is>
+      </c>
+      <c r="N442" t="inlineStr">
+        <is>
+          <t>-38.214074344655344,178.33337061738567</t>
+        </is>
+      </c>
+      <c r="O442" t="inlineStr">
+        <is>
+          <t>-38.21480018979896,178.3333158689272</t>
+        </is>
+      </c>
+      <c r="P442" t="inlineStr">
+        <is>
+          <t>-38.21552680546571,178.33333386436007</t>
+        </is>
+      </c>
+      <c r="Q442" t="inlineStr">
+        <is>
+          <t>-38.21626034451135,178.3334393136954</t>
+        </is>
+      </c>
+      <c r="R442" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0249/nzd0249.xlsx
+++ b/data/nzd0249/nzd0249.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R442"/>
+  <dimension ref="A1:R444"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26952,6 +26952,126 @@
         <v>320.71</v>
       </c>
       <c r="R442" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-22 21:53:36+00:00</t>
+        </is>
+      </c>
+      <c r="B443" t="n">
+        <v>306.2</v>
+      </c>
+      <c r="C443" t="n">
+        <v>306.53</v>
+      </c>
+      <c r="D443" t="n">
+        <v>313.81</v>
+      </c>
+      <c r="E443" t="n">
+        <v>312.85</v>
+      </c>
+      <c r="F443" t="n">
+        <v>318.5</v>
+      </c>
+      <c r="G443" t="n">
+        <v>323.97</v>
+      </c>
+      <c r="H443" t="n">
+        <v>331.43</v>
+      </c>
+      <c r="I443" t="n">
+        <v>336.33</v>
+      </c>
+      <c r="J443" t="n">
+        <v>334.75</v>
+      </c>
+      <c r="K443" t="n">
+        <v>328.16</v>
+      </c>
+      <c r="L443" t="n">
+        <v>323.57</v>
+      </c>
+      <c r="M443" t="n">
+        <v>324.1</v>
+      </c>
+      <c r="N443" t="n">
+        <v>334.5</v>
+      </c>
+      <c r="O443" t="n">
+        <v>349.05</v>
+      </c>
+      <c r="P443" t="n">
+        <v>335.22</v>
+      </c>
+      <c r="Q443" t="n">
+        <v>319.23</v>
+      </c>
+      <c r="R443" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-30 21:53:27+00:00</t>
+        </is>
+      </c>
+      <c r="B444" t="n">
+        <v>307.45</v>
+      </c>
+      <c r="C444" t="n">
+        <v>307.37</v>
+      </c>
+      <c r="D444" t="n">
+        <v>314.09</v>
+      </c>
+      <c r="E444" t="n">
+        <v>313.51</v>
+      </c>
+      <c r="F444" t="n">
+        <v>319.28</v>
+      </c>
+      <c r="G444" t="n">
+        <v>325.38</v>
+      </c>
+      <c r="H444" t="n">
+        <v>332.71</v>
+      </c>
+      <c r="I444" t="n">
+        <v>336.78</v>
+      </c>
+      <c r="J444" t="n">
+        <v>335.56</v>
+      </c>
+      <c r="K444" t="n">
+        <v>328.97</v>
+      </c>
+      <c r="L444" t="n">
+        <v>324.25</v>
+      </c>
+      <c r="M444" t="n">
+        <v>324.44</v>
+      </c>
+      <c r="N444" t="n">
+        <v>334.11</v>
+      </c>
+      <c r="O444" t="n">
+        <v>347.74</v>
+      </c>
+      <c r="P444" t="n">
+        <v>333.14</v>
+      </c>
+      <c r="Q444" t="n">
+        <v>316.26</v>
+      </c>
+      <c r="R444" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -26968,7 +27088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B444"/>
+  <dimension ref="A1:B446"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31411,6 +31531,26 @@
       </c>
       <c r="B444" t="n">
         <v>-0.33</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>2026-07-22 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B445" t="n">
+        <v>-0.08</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>2026-07-30 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B446" t="n">
+        <v>0.02</v>
       </c>
     </row>
   </sheetData>
@@ -31579,28 +31719,28 @@
         <v>0.0823</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.02173484726003266</v>
+        <v>-0.02640540908481627</v>
       </c>
       <c r="J2" t="n">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="K2" t="n">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0003237703801177716</v>
+        <v>0.0004823801442701559</v>
       </c>
       <c r="M2" t="n">
-        <v>7.243716581890233</v>
+        <v>7.232179676771215</v>
       </c>
       <c r="N2" t="n">
-        <v>83.81163834062525</v>
+        <v>83.54710756011816</v>
       </c>
       <c r="O2" t="n">
-        <v>9.15486965175503</v>
+        <v>9.140410688810332</v>
       </c>
       <c r="P2" t="n">
-        <v>312.4721963638281</v>
+        <v>312.5203291179228</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -31657,28 +31797,28 @@
         <v>0.08450000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.05193313746134808</v>
+        <v>0.04624418970102422</v>
       </c>
       <c r="J3" t="n">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="K3" t="n">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002842041948228791</v>
+        <v>0.002272423773790888</v>
       </c>
       <c r="M3" t="n">
-        <v>5.8400317979106</v>
+        <v>5.84105210474441</v>
       </c>
       <c r="N3" t="n">
-        <v>54.37402616039387</v>
+        <v>54.29771919014458</v>
       </c>
       <c r="O3" t="n">
-        <v>7.373874569071125</v>
+        <v>7.36869860899091</v>
       </c>
       <c r="P3" t="n">
-        <v>311.714076051188</v>
+        <v>311.7727053192098</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -31735,28 +31875,28 @@
         <v>0.059</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1991660112257905</v>
+        <v>0.1973002424995514</v>
       </c>
       <c r="J4" t="n">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="K4" t="n">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="L4" t="n">
-        <v>0.06189143636458649</v>
+        <v>0.06140576328547809</v>
       </c>
       <c r="M4" t="n">
-        <v>4.783170217530283</v>
+        <v>4.770589249420358</v>
       </c>
       <c r="N4" t="n">
-        <v>34.40498339380943</v>
+        <v>34.26758283972802</v>
       </c>
       <c r="O4" t="n">
-        <v>5.865576134857465</v>
+        <v>5.853851965990259</v>
       </c>
       <c r="P4" t="n">
-        <v>310.5946404728918</v>
+        <v>310.6138949728042</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -31813,28 +31953,28 @@
         <v>0.09429999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1280888288997807</v>
+        <v>0.123668099216835</v>
       </c>
       <c r="J5" t="n">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="K5" t="n">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01658569052462167</v>
+        <v>0.01561748040228828</v>
       </c>
       <c r="M5" t="n">
-        <v>5.901207311214059</v>
+        <v>5.899212687089878</v>
       </c>
       <c r="N5" t="n">
-        <v>55.66649002172031</v>
+        <v>55.51722870526594</v>
       </c>
       <c r="O5" t="n">
-        <v>7.460997923985793</v>
+        <v>7.450988438137985</v>
       </c>
       <c r="P5" t="n">
-        <v>314.5127330411277</v>
+        <v>314.558354404641</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31891,28 +32031,28 @@
         <v>0.0727</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1349687429051611</v>
+        <v>0.1296842947100183</v>
       </c>
       <c r="J6" t="n">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="K6" t="n">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01584325512209594</v>
+        <v>0.01477065995338622</v>
       </c>
       <c r="M6" t="n">
-        <v>5.9497739379227</v>
+        <v>5.955543370526255</v>
       </c>
       <c r="N6" t="n">
-        <v>64.75221453552786</v>
+        <v>64.60582693303569</v>
       </c>
       <c r="O6" t="n">
-        <v>8.04687607308127</v>
+        <v>8.037774998905835</v>
       </c>
       <c r="P6" t="n">
-        <v>320.9714159379242</v>
+        <v>321.0259508041431</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31969,28 +32109,28 @@
         <v>0.0653</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2858217192464414</v>
+        <v>0.2784470479840503</v>
       </c>
       <c r="J7" t="n">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="K7" t="n">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08313584429028131</v>
+        <v>0.07962738187935947</v>
       </c>
       <c r="M7" t="n">
-        <v>5.425455003484668</v>
+        <v>5.442024900927584</v>
       </c>
       <c r="N7" t="n">
-        <v>51.90755272013408</v>
+        <v>51.96251180535102</v>
       </c>
       <c r="O7" t="n">
-        <v>7.204689633851973</v>
+        <v>7.208502743659811</v>
       </c>
       <c r="P7" t="n">
-        <v>324.9972483102602</v>
+        <v>325.0729602193339</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -32047,28 +32187,28 @@
         <v>0.0597</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2623792979190482</v>
+        <v>0.2551216630551443</v>
       </c>
       <c r="J8" t="n">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="K8" t="n">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="L8" t="n">
-        <v>0.08685843444625196</v>
+        <v>0.08282980455643418</v>
       </c>
       <c r="M8" t="n">
-        <v>5.034443399477302</v>
+        <v>5.049645524693482</v>
       </c>
       <c r="N8" t="n">
-        <v>41.69736990388904</v>
+        <v>41.78896533555715</v>
       </c>
       <c r="O8" t="n">
-        <v>6.457350068246962</v>
+        <v>6.464438516650704</v>
       </c>
       <c r="P8" t="n">
-        <v>332.9019818988018</v>
+        <v>332.9764924986916</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -32125,28 +32265,28 @@
         <v>0.0568</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1633183622190714</v>
+        <v>0.1611911246727039</v>
       </c>
       <c r="J9" t="n">
+        <v>443</v>
+      </c>
+      <c r="K9" t="n">
         <v>441</v>
       </c>
-      <c r="K9" t="n">
-        <v>439</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.03953523791003921</v>
+        <v>0.03893368126232022</v>
       </c>
       <c r="M9" t="n">
-        <v>4.794558705311379</v>
+        <v>4.785523862142419</v>
       </c>
       <c r="N9" t="n">
-        <v>37.48810507066019</v>
+        <v>37.34233512707296</v>
       </c>
       <c r="O9" t="n">
-        <v>6.122753063015051</v>
+        <v>6.110837514373375</v>
       </c>
       <c r="P9" t="n">
-        <v>334.4661926854775</v>
+        <v>334.4880014696422</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -32203,28 +32343,28 @@
         <v>0.0615</v>
       </c>
       <c r="I10" t="n">
-        <v>0.142628331379719</v>
+        <v>0.1430195607698808</v>
       </c>
       <c r="J10" t="n">
+        <v>443</v>
+      </c>
+      <c r="K10" t="n">
         <v>441</v>
       </c>
-      <c r="K10" t="n">
-        <v>439</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.02932093292180982</v>
+        <v>0.02978989147897704</v>
       </c>
       <c r="M10" t="n">
-        <v>4.769485680551765</v>
+        <v>4.749644204330728</v>
       </c>
       <c r="N10" t="n">
-        <v>38.9615171094815</v>
+        <v>38.78636560996778</v>
       </c>
       <c r="O10" t="n">
-        <v>6.241916140856227</v>
+        <v>6.227870070093609</v>
       </c>
       <c r="P10" t="n">
-        <v>330.8828890252136</v>
+        <v>330.8788762081262</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32281,28 +32421,28 @@
         <v>0.0587</v>
       </c>
       <c r="I11" t="n">
-        <v>0.04381608199642092</v>
+        <v>0.04936027798918901</v>
       </c>
       <c r="J11" t="n">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="K11" t="n">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="L11" t="n">
-        <v>0.002056656527912759</v>
+        <v>0.002629199374222457</v>
       </c>
       <c r="M11" t="n">
-        <v>6.06238587076793</v>
+        <v>6.061597295031865</v>
       </c>
       <c r="N11" t="n">
-        <v>53.67037317177443</v>
+        <v>53.59101348354859</v>
       </c>
       <c r="O11" t="n">
-        <v>7.326006631977235</v>
+        <v>7.320588329058573</v>
       </c>
       <c r="P11" t="n">
-        <v>321.3410608145588</v>
+        <v>321.2841375304992</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -32359,28 +32499,28 @@
         <v>0.0634</v>
       </c>
       <c r="I12" t="n">
-        <v>0.06284045900597923</v>
+        <v>0.06890162513555438</v>
       </c>
       <c r="J12" t="n">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="K12" t="n">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="L12" t="n">
-        <v>0.003398950987416938</v>
+        <v>0.004116123431231022</v>
       </c>
       <c r="M12" t="n">
-        <v>6.683654225410669</v>
+        <v>6.682923126475147</v>
       </c>
       <c r="N12" t="n">
-        <v>66.70809696968196</v>
+        <v>66.60132811283611</v>
       </c>
       <c r="O12" t="n">
-        <v>8.167502492787007</v>
+        <v>8.160963675500346</v>
       </c>
       <c r="P12" t="n">
-        <v>315.6127700052929</v>
+        <v>315.5505393181168</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -32437,28 +32577,28 @@
         <v>0.0605</v>
       </c>
       <c r="I13" t="n">
-        <v>0.001723551453895447</v>
+        <v>0.009200489156626485</v>
       </c>
       <c r="J13" t="n">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="K13" t="n">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="L13" t="n">
-        <v>1.824541773443045e-06</v>
+        <v>5.239380564114882e-05</v>
       </c>
       <c r="M13" t="n">
-        <v>7.92770106239241</v>
+        <v>7.927747790776261</v>
       </c>
       <c r="N13" t="n">
-        <v>93.80312764904191</v>
+        <v>93.67480186197811</v>
       </c>
       <c r="O13" t="n">
-        <v>9.685201476946254</v>
+        <v>9.678574371361627</v>
       </c>
       <c r="P13" t="n">
-        <v>316.0776885976365</v>
+        <v>316.000923076316</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -32515,28 +32655,28 @@
         <v>0.0692</v>
       </c>
       <c r="I14" t="n">
-        <v>0.06991237687653848</v>
+        <v>0.07772382683660389</v>
       </c>
       <c r="J14" t="n">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="K14" t="n">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="L14" t="n">
-        <v>0.003470969791316669</v>
+        <v>0.00431611159969969</v>
       </c>
       <c r="M14" t="n">
-        <v>7.031369921065986</v>
+        <v>7.038279852239026</v>
       </c>
       <c r="N14" t="n">
-        <v>80.84825901114328</v>
+        <v>80.80547962468496</v>
       </c>
       <c r="O14" t="n">
-        <v>8.991565993259643</v>
+        <v>8.989186816652825</v>
       </c>
       <c r="P14" t="n">
-        <v>323.903173329009</v>
+        <v>323.8229749398366</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -32593,28 +32733,28 @@
         <v>0.07530000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>0.145066425666182</v>
+        <v>0.1551365367792492</v>
       </c>
       <c r="J15" t="n">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="K15" t="n">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="L15" t="n">
-        <v>0.01282298879461019</v>
+        <v>0.01471272689244574</v>
       </c>
       <c r="M15" t="n">
-        <v>7.619862689911382</v>
+        <v>7.63539818331469</v>
       </c>
       <c r="N15" t="n">
-        <v>93.33897078465949</v>
+        <v>93.45478252172771</v>
       </c>
       <c r="O15" t="n">
-        <v>9.661209592212535</v>
+        <v>9.667201380013127</v>
       </c>
       <c r="P15" t="n">
-        <v>333.5124882630843</v>
+        <v>333.4091024121915</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -32671,28 +32811,28 @@
         <v>0.0862</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1556914388810349</v>
+        <v>0.1651018593988466</v>
       </c>
       <c r="J16" t="n">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="K16" t="n">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="L16" t="n">
-        <v>0.01418989303707452</v>
+        <v>0.01602401439548085</v>
       </c>
       <c r="M16" t="n">
-        <v>7.699191824815121</v>
+        <v>7.709792061769995</v>
       </c>
       <c r="N16" t="n">
-        <v>97.02128575475605</v>
+        <v>97.05563354758181</v>
       </c>
       <c r="O16" t="n">
-        <v>9.849938362992738</v>
+        <v>9.851681762398835</v>
       </c>
       <c r="P16" t="n">
-        <v>319.7301656970576</v>
+        <v>319.633554424811</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -32749,28 +32889,28 @@
         <v>0.0844</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2330854956462788</v>
+        <v>0.237647599238386</v>
       </c>
       <c r="J17" t="n">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="K17" t="n">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="L17" t="n">
-        <v>0.03609003786373932</v>
+        <v>0.03780678555668504</v>
       </c>
       <c r="M17" t="n">
-        <v>7.27142974931463</v>
+        <v>7.260667600077366</v>
       </c>
       <c r="N17" t="n">
-        <v>83.59937795482071</v>
+        <v>83.34183256590001</v>
       </c>
       <c r="O17" t="n">
-        <v>9.143269544031867</v>
+        <v>9.129174802023456</v>
       </c>
       <c r="P17" t="n">
-        <v>306.4861174909319</v>
+        <v>306.439285161441</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -32808,7 +32948,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R442"/>
+  <dimension ref="A1:R444"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73423,6 +73563,190 @@
         </is>
       </c>
     </row>
+    <row r="443">
+      <c r="A443" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-22 21:53:36+00:00</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>-38.20573674410026,178.33373016376308</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>-38.20644201919857,178.33376418814186</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>-38.20714282755394,178.3338771810289</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>-38.207848916730136,178.33389654872</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>-38.20855075722119,178.3339910228659</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>-38.20923512384097,178.33408381389165</t>
+        </is>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>-38.209923739151066,178.33409575010955</t>
+        </is>
+      </c>
+      <c r="I443" t="inlineStr">
+        <is>
+          <t>-38.210628890141145,178.33407515063664</t>
+        </is>
+      </c>
+      <c r="J443" t="inlineStr">
+        <is>
+          <t>-38.21133150314315,178.3339807787914</t>
+        </is>
+      </c>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>-38.212025075508045,178.33383055177066</t>
+        </is>
+      </c>
+      <c r="L443" t="inlineStr">
+        <is>
+          <t>-38.212696470765344,178.3336601162373</t>
+        </is>
+      </c>
+      <c r="M443" t="inlineStr">
+        <is>
+          <t>-38.21336880469014,178.3334593403601</t>
+        </is>
+      </c>
+      <c r="N443" t="inlineStr">
+        <is>
+          <t>-38.2140733306449,178.33336425210197</t>
+        </is>
+      </c>
+      <c r="O443" t="inlineStr">
+        <is>
+          <t>-38.21480022948039,178.33330869174094</t>
+        </is>
+      </c>
+      <c r="P443" t="inlineStr">
+        <is>
+          <t>-38.21553154802802,178.33331342554118</t>
+        </is>
+      </c>
+      <c r="Q443" t="inlineStr">
+        <is>
+          <t>-38.21626491877889,178.3334234804268</t>
+        </is>
+      </c>
+      <c r="R443" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-30 21:53:27+00:00</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>-38.205735941985495,178.33374436644775</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>-38.20644148017037,178.3337737324376</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>-38.207142647873404,178.33388036249073</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>-38.20784849319253,178.33390404795225</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>-38.20855025666542,178.3339998856786</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>-38.209234958340474,178.33409987490037</t>
+        </is>
+      </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>-38.20992427148624,178.33411031608057</t>
+        </is>
+      </c>
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>-38.21062908108357,178.33408027131068</t>
+        </is>
+      </c>
+      <c r="J444" t="inlineStr">
+        <is>
+          <t>-38.211331846839585,178.33398999609463</t>
+        </is>
+      </c>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>-38.21202561133637,178.3338397544263</t>
+        </is>
+      </c>
+      <c r="L444" t="inlineStr">
+        <is>
+          <t>-38.21269738273779,178.3336677762869</t>
+        </is>
+      </c>
+      <c r="M444" t="inlineStr">
+        <is>
+          <t>-38.21336940953991,178.33346313715845</t>
+        </is>
+      </c>
+      <c r="N444" t="inlineStr">
+        <is>
+          <t>-38.21407263684809,178.33335989690795</t>
+        </is>
+      </c>
+      <c r="O444" t="inlineStr">
+        <is>
+          <t>-38.21480031199119,178.33329376775032</t>
+        </is>
+      </c>
+      <c r="P444" t="inlineStr">
+        <is>
+          <t>-38.21553682317356,178.3332906914503</t>
+        </is>
+      </c>
+      <c r="Q444" t="inlineStr">
+        <is>
+          <t>-38.216274098215145,178.3333917069014</t>
+        </is>
+      </c>
+      <c r="R444" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0249/nzd0249.xlsx
+++ b/data/nzd0249/nzd0249.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R444"/>
+  <dimension ref="A1:R447"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27072,6 +27072,186 @@
         <v>316.26</v>
       </c>
       <c r="R444" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-23 21:53:27+00:00</t>
+        </is>
+      </c>
+      <c r="B445" t="n">
+        <v>311.46</v>
+      </c>
+      <c r="C445" t="n">
+        <v>310.97</v>
+      </c>
+      <c r="D445" t="n">
+        <v>316.35</v>
+      </c>
+      <c r="E445" t="n">
+        <v>316.34</v>
+      </c>
+      <c r="F445" t="n">
+        <v>322.2</v>
+      </c>
+      <c r="G445" t="n">
+        <v>328.26</v>
+      </c>
+      <c r="H445" t="n">
+        <v>335.32</v>
+      </c>
+      <c r="I445" t="n">
+        <v>339.16</v>
+      </c>
+      <c r="J445" t="n">
+        <v>336.78</v>
+      </c>
+      <c r="K445" t="n">
+        <v>330.07</v>
+      </c>
+      <c r="L445" t="n">
+        <v>323.2</v>
+      </c>
+      <c r="M445" t="n">
+        <v>323.57</v>
+      </c>
+      <c r="N445" t="n">
+        <v>332.54</v>
+      </c>
+      <c r="O445" t="n">
+        <v>344.42</v>
+      </c>
+      <c r="P445" t="n">
+        <v>330.18</v>
+      </c>
+      <c r="Q445" t="n">
+        <v>313.56</v>
+      </c>
+      <c r="R445" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-08 21:53:54+00:00</t>
+        </is>
+      </c>
+      <c r="B446" t="n">
+        <v>315.72</v>
+      </c>
+      <c r="C446" t="n">
+        <v>314.76</v>
+      </c>
+      <c r="D446" t="n">
+        <v>317.69</v>
+      </c>
+      <c r="E446" t="n">
+        <v>317.3</v>
+      </c>
+      <c r="F446" t="n">
+        <v>322.97</v>
+      </c>
+      <c r="G446" t="n">
+        <v>329.15</v>
+      </c>
+      <c r="H446" t="n">
+        <v>336.12</v>
+      </c>
+      <c r="I446" t="n">
+        <v>339.32</v>
+      </c>
+      <c r="J446" t="n">
+        <v>336.3</v>
+      </c>
+      <c r="K446" t="n">
+        <v>330.28</v>
+      </c>
+      <c r="L446" t="n">
+        <v>322.07</v>
+      </c>
+      <c r="M446" t="n">
+        <v>321.7</v>
+      </c>
+      <c r="N446" t="n">
+        <v>329.49</v>
+      </c>
+      <c r="O446" t="n">
+        <v>340.12</v>
+      </c>
+      <c r="P446" t="n">
+        <v>325.72</v>
+      </c>
+      <c r="Q446" t="n">
+        <v>309.05</v>
+      </c>
+      <c r="R446" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-16 21:53:38+00:00</t>
+        </is>
+      </c>
+      <c r="B447" t="n">
+        <v>317.74</v>
+      </c>
+      <c r="C447" t="n">
+        <v>316.15</v>
+      </c>
+      <c r="D447" t="n">
+        <v>319.56</v>
+      </c>
+      <c r="E447" t="n">
+        <v>319.71</v>
+      </c>
+      <c r="F447" t="n">
+        <v>325.14</v>
+      </c>
+      <c r="G447" t="n">
+        <v>330.98</v>
+      </c>
+      <c r="H447" t="n">
+        <v>337.89</v>
+      </c>
+      <c r="I447" t="n">
+        <v>341.24</v>
+      </c>
+      <c r="J447" t="n">
+        <v>337.97</v>
+      </c>
+      <c r="K447" t="n">
+        <v>331.4</v>
+      </c>
+      <c r="L447" t="n">
+        <v>322.99</v>
+      </c>
+      <c r="M447" t="n">
+        <v>322.69</v>
+      </c>
+      <c r="N447" t="n">
+        <v>328.75</v>
+      </c>
+      <c r="O447" t="n">
+        <v>338.68</v>
+      </c>
+      <c r="P447" t="n">
+        <v>323.82</v>
+      </c>
+      <c r="Q447" t="n">
+        <v>306.82</v>
+      </c>
+      <c r="R447" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -27088,7 +27268,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B446"/>
+  <dimension ref="A1:B449"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31551,6 +31731,36 @@
       </c>
       <c r="B446" t="n">
         <v>0.02</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>2026-08-23 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B447" t="n">
+        <v>-0.41</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>2026-09-08 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B448" t="n">
+        <v>-0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>2026-09-16 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B449" t="n">
+        <v>0.63</v>
       </c>
     </row>
   </sheetData>
@@ -31719,28 +31929,28 @@
         <v>0.0823</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.02640540908481627</v>
+        <v>-0.0220697090669218</v>
       </c>
       <c r="J2" t="n">
+        <v>446</v>
+      </c>
+      <c r="K2" t="n">
         <v>443</v>
       </c>
-      <c r="K2" t="n">
-        <v>440</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.0004823801442701559</v>
+        <v>0.0003421035142160411</v>
       </c>
       <c r="M2" t="n">
-        <v>7.232179676771215</v>
+        <v>7.2075051927557</v>
       </c>
       <c r="N2" t="n">
-        <v>83.54710756011816</v>
+        <v>83.09420142858593</v>
       </c>
       <c r="O2" t="n">
-        <v>9.140410688810332</v>
+        <v>9.115602088100704</v>
       </c>
       <c r="P2" t="n">
-        <v>312.5203291179228</v>
+        <v>312.4753998683637</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -31797,28 +32007,28 @@
         <v>0.08450000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04624418970102422</v>
+        <v>0.04753068681151806</v>
       </c>
       <c r="J3" t="n">
+        <v>446</v>
+      </c>
+      <c r="K3" t="n">
         <v>443</v>
       </c>
-      <c r="K3" t="n">
-        <v>440</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.002272423773790888</v>
+        <v>0.002438000156342879</v>
       </c>
       <c r="M3" t="n">
-        <v>5.84105210474441</v>
+        <v>5.817138731110719</v>
       </c>
       <c r="N3" t="n">
-        <v>54.29771919014458</v>
+        <v>53.96820635366078</v>
       </c>
       <c r="O3" t="n">
-        <v>7.36869860899091</v>
+        <v>7.346305626208371</v>
       </c>
       <c r="P3" t="n">
-        <v>311.7727053192098</v>
+        <v>311.7593517683094</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -31875,28 +32085,28 @@
         <v>0.059</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1973002424995514</v>
+        <v>0.1999171203440775</v>
       </c>
       <c r="J4" t="n">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="K4" t="n">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="L4" t="n">
-        <v>0.06140576328547809</v>
+        <v>0.06385074945775371</v>
       </c>
       <c r="M4" t="n">
-        <v>4.770589249420358</v>
+        <v>4.751134523675338</v>
       </c>
       <c r="N4" t="n">
-        <v>34.26758283972802</v>
+        <v>34.07223710206248</v>
       </c>
       <c r="O4" t="n">
-        <v>5.853851965990259</v>
+        <v>5.837142888611043</v>
       </c>
       <c r="P4" t="n">
-        <v>310.6138949728042</v>
+        <v>310.586746358506</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -31953,28 +32163,28 @@
         <v>0.09429999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.123668099216835</v>
+        <v>0.1235046068423431</v>
       </c>
       <c r="J5" t="n">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="K5" t="n">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01561748040228828</v>
+        <v>0.01582569534577094</v>
       </c>
       <c r="M5" t="n">
-        <v>5.899212687089878</v>
+        <v>5.868472390180297</v>
       </c>
       <c r="N5" t="n">
-        <v>55.51722870526594</v>
+        <v>55.15655279747252</v>
       </c>
       <c r="O5" t="n">
-        <v>7.450988438137985</v>
+        <v>7.426745774393555</v>
       </c>
       <c r="P5" t="n">
-        <v>314.558354404641</v>
+        <v>314.5600292717145</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32031,28 +32241,28 @@
         <v>0.0727</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1296842947100183</v>
+        <v>0.12818235255662</v>
       </c>
       <c r="J6" t="n">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="K6" t="n">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01477065995338622</v>
+        <v>0.01466571624318236</v>
       </c>
       <c r="M6" t="n">
-        <v>5.955543370526255</v>
+        <v>5.927399242872267</v>
       </c>
       <c r="N6" t="n">
-        <v>64.60582693303569</v>
+        <v>64.18866918828606</v>
       </c>
       <c r="O6" t="n">
-        <v>8.037774998905835</v>
+        <v>8.011783146608877</v>
       </c>
       <c r="P6" t="n">
-        <v>321.0259508041431</v>
+        <v>321.04150393024</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32109,28 +32319,28 @@
         <v>0.0653</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2784470479840503</v>
+        <v>0.2741717950872901</v>
       </c>
       <c r="J7" t="n">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="K7" t="n">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="L7" t="n">
-        <v>0.07962738187935947</v>
+        <v>0.07845694007720205</v>
       </c>
       <c r="M7" t="n">
-        <v>5.442024900927584</v>
+        <v>5.429538466923019</v>
       </c>
       <c r="N7" t="n">
-        <v>51.96251180535102</v>
+        <v>51.68676839805325</v>
       </c>
       <c r="O7" t="n">
-        <v>7.208502743659811</v>
+        <v>7.189351041509466</v>
       </c>
       <c r="P7" t="n">
-        <v>325.0729602193339</v>
+        <v>325.117037496407</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -32187,28 +32397,28 @@
         <v>0.0597</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2551216630551443</v>
+        <v>0.2504513405679778</v>
       </c>
       <c r="J8" t="n">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="K8" t="n">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="L8" t="n">
-        <v>0.08282980455643418</v>
+        <v>0.08112059179084141</v>
       </c>
       <c r="M8" t="n">
-        <v>5.049645524693482</v>
+        <v>5.040569696001608</v>
       </c>
       <c r="N8" t="n">
-        <v>41.78896533555715</v>
+        <v>41.59333003853923</v>
       </c>
       <c r="O8" t="n">
-        <v>6.464438516650704</v>
+        <v>6.44928911109893</v>
       </c>
       <c r="P8" t="n">
-        <v>332.9764924986916</v>
+        <v>333.0246453851935</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -32265,28 +32475,28 @@
         <v>0.0568</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1611911246727039</v>
+        <v>0.1626245966379294</v>
       </c>
       <c r="J9" t="n">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="K9" t="n">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03893368126232022</v>
+        <v>0.04021141530384875</v>
       </c>
       <c r="M9" t="n">
-        <v>4.785523862142419</v>
+        <v>4.758686743323125</v>
       </c>
       <c r="N9" t="n">
-        <v>37.34233512707296</v>
+        <v>37.10334921951997</v>
       </c>
       <c r="O9" t="n">
-        <v>6.110837514373375</v>
+        <v>6.091251859800247</v>
       </c>
       <c r="P9" t="n">
-        <v>334.4880014696422</v>
+        <v>334.4732254661214</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -32343,28 +32553,28 @@
         <v>0.0615</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1430195607698808</v>
+        <v>0.1460935200907219</v>
       </c>
       <c r="J10" t="n">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="K10" t="n">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02978989147897704</v>
+        <v>0.03150790315727892</v>
       </c>
       <c r="M10" t="n">
-        <v>4.749644204330728</v>
+        <v>4.731534721144965</v>
       </c>
       <c r="N10" t="n">
-        <v>38.78636560996778</v>
+        <v>38.56141075063569</v>
       </c>
       <c r="O10" t="n">
-        <v>6.227870070093609</v>
+        <v>6.209783470511327</v>
       </c>
       <c r="P10" t="n">
-        <v>330.8788762081262</v>
+        <v>330.8472095675643</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32421,28 +32631,28 @@
         <v>0.0587</v>
       </c>
       <c r="I11" t="n">
-        <v>0.04936027798918901</v>
+        <v>0.06017491865003077</v>
       </c>
       <c r="J11" t="n">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="K11" t="n">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="L11" t="n">
-        <v>0.002629199374222457</v>
+        <v>0.003935527470745104</v>
       </c>
       <c r="M11" t="n">
-        <v>6.061597295031865</v>
+        <v>6.072413318194248</v>
       </c>
       <c r="N11" t="n">
-        <v>53.59101348354859</v>
+        <v>53.64942694276812</v>
       </c>
       <c r="O11" t="n">
-        <v>7.320588329058573</v>
+        <v>7.324576912202378</v>
       </c>
       <c r="P11" t="n">
-        <v>321.2841375304992</v>
+        <v>321.1725914586805</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -32499,28 +32709,28 @@
         <v>0.0634</v>
       </c>
       <c r="I12" t="n">
-        <v>0.06890162513555438</v>
+        <v>0.07614842402183673</v>
       </c>
       <c r="J12" t="n">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="K12" t="n">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="L12" t="n">
-        <v>0.004116123431231022</v>
+        <v>0.005090560830438573</v>
       </c>
       <c r="M12" t="n">
-        <v>6.682923126475147</v>
+        <v>6.673160176860379</v>
       </c>
       <c r="N12" t="n">
-        <v>66.60132811283611</v>
+        <v>66.34211621805839</v>
       </c>
       <c r="O12" t="n">
-        <v>8.160963675500346</v>
+        <v>8.145066986714006</v>
       </c>
       <c r="P12" t="n">
-        <v>315.5505393181168</v>
+        <v>315.4758010717055</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -32577,28 +32787,28 @@
         <v>0.0605</v>
       </c>
       <c r="I13" t="n">
-        <v>0.009200489156626485</v>
+        <v>0.01789968126094052</v>
       </c>
       <c r="J13" t="n">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="K13" t="n">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="L13" t="n">
-        <v>5.239380564114882e-05</v>
+        <v>0.0002009489638412632</v>
       </c>
       <c r="M13" t="n">
-        <v>7.927747790776261</v>
+        <v>7.915662555115558</v>
       </c>
       <c r="N13" t="n">
-        <v>93.67480186197811</v>
+        <v>93.31836178937719</v>
       </c>
       <c r="O13" t="n">
-        <v>9.678574371361627</v>
+        <v>9.660142948703047</v>
       </c>
       <c r="P13" t="n">
-        <v>316.000923076316</v>
+        <v>315.911210077971</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -32655,28 +32865,28 @@
         <v>0.0692</v>
       </c>
       <c r="I14" t="n">
-        <v>0.07772382683660389</v>
+        <v>0.08359729067325343</v>
       </c>
       <c r="J14" t="n">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="K14" t="n">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="L14" t="n">
-        <v>0.00431611159969969</v>
+        <v>0.005062399206324453</v>
       </c>
       <c r="M14" t="n">
-        <v>7.038279852239026</v>
+        <v>7.019598894773197</v>
       </c>
       <c r="N14" t="n">
-        <v>80.80547962468496</v>
+        <v>80.4032162653708</v>
       </c>
       <c r="O14" t="n">
-        <v>8.989186816652825</v>
+        <v>8.966784053682279</v>
       </c>
       <c r="P14" t="n">
-        <v>323.8229749398366</v>
+        <v>323.7624232982808</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -32733,28 +32943,28 @@
         <v>0.07530000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1551365367792492</v>
+        <v>0.1598300874884147</v>
       </c>
       <c r="J15" t="n">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="K15" t="n">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="L15" t="n">
-        <v>0.01471272689244574</v>
+        <v>0.01583464990765693</v>
       </c>
       <c r="M15" t="n">
-        <v>7.63539818331469</v>
+        <v>7.607050565634436</v>
       </c>
       <c r="N15" t="n">
-        <v>93.45478252172771</v>
+        <v>92.9450447784608</v>
       </c>
       <c r="O15" t="n">
-        <v>9.667201380013127</v>
+        <v>9.640801044439243</v>
       </c>
       <c r="P15" t="n">
-        <v>333.4091024121915</v>
+        <v>333.3607325636866</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -32811,28 +33021,28 @@
         <v>0.0862</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1651018593988466</v>
+        <v>0.1684482383981413</v>
       </c>
       <c r="J16" t="n">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="K16" t="n">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="L16" t="n">
-        <v>0.01602401439548085</v>
+        <v>0.01692324267172896</v>
       </c>
       <c r="M16" t="n">
-        <v>7.709792061769995</v>
+        <v>7.675573696219317</v>
       </c>
       <c r="N16" t="n">
-        <v>97.05563354758181</v>
+        <v>96.49089956670781</v>
       </c>
       <c r="O16" t="n">
-        <v>9.851681762398835</v>
+        <v>9.822978141414538</v>
       </c>
       <c r="P16" t="n">
-        <v>319.633554424811</v>
+        <v>319.5990825203118</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -32889,28 +33099,28 @@
         <v>0.0844</v>
       </c>
       <c r="I17" t="n">
-        <v>0.237647599238386</v>
+        <v>0.2334755686521078</v>
       </c>
       <c r="J17" t="n">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="K17" t="n">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="L17" t="n">
-        <v>0.03780678555668504</v>
+        <v>0.03706759349835509</v>
       </c>
       <c r="M17" t="n">
-        <v>7.260667600077366</v>
+        <v>7.235726252226464</v>
       </c>
       <c r="N17" t="n">
-        <v>83.34183256590001</v>
+        <v>82.89605376216522</v>
       </c>
       <c r="O17" t="n">
-        <v>9.129174802023456</v>
+        <v>9.10472700096852</v>
       </c>
       <c r="P17" t="n">
-        <v>306.439285161441</v>
+        <v>306.4823577097413</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -32948,7 +33158,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R444"/>
+  <dimension ref="A1:R447"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73747,6 +73957,282 @@
         </is>
       </c>
     </row>
+    <row r="445">
+      <c r="A445" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-23 21:53:27+00:00</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>-38.20573336878982,178.33378992865673</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>-38.20643917004077,178.33381463655962</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>-38.20714119759169,178.33390604143173</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>-38.20784667710923,178.33393620374952</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>-38.20854838278405,178.33403306441153</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>-38.20923462029008,178.33413268036392</t>
+        </is>
+      </c>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>-38.20992535694528,178.33414001700586</t>
+        </is>
+      </c>
+      <c r="I445" t="inlineStr">
+        <is>
+          <t>-38.210630090953124,178.33410735398667</t>
+        </is>
+      </c>
+      <c r="J445" t="inlineStr">
+        <is>
+          <t>-38.2113323645044,178.3340038789464</t>
+        </is>
+      </c>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>-38.2120263390033,178.33385225185995</t>
+        </is>
+      </c>
+      <c r="L445" t="inlineStr">
+        <is>
+          <t>-38.21269597454483,178.33365594826918</t>
+        </is>
+      </c>
+      <c r="M445" t="inlineStr">
+        <is>
+          <t>-38.21336786183584,178.33345342182162</t>
+        </is>
+      </c>
+      <c r="N445" t="inlineStr">
+        <is>
+          <t>-38.21406984386946,178.33334236446083</t>
+        </is>
+      </c>
+      <c r="O445" t="inlineStr">
+        <is>
+          <t>-38.214800521093956,178.3332559451164</t>
+        </is>
+      </c>
+      <c r="P445" t="inlineStr">
+        <is>
+          <t>-38.21554433010424,178.33325833908367</t>
+        </is>
+      </c>
+      <c r="Q445" t="inlineStr">
+        <is>
+          <t>-38.216282443150185,178.33336282187062</t>
+        </is>
+      </c>
+      <c r="R445" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-08 21:53:54+00:00</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>-38.20573063515129,178.33383833139658</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>-38.20643673797239,178.3338576995057</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>-38.20714033768752,178.33392126699772</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>-38.207846061050724,178.33394711172255</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>-38.208547888642556,178.33404181359745</t>
+        </is>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>-38.209234515821265,178.33414281816314</t>
+        </is>
+      </c>
+      <c r="H446" t="inlineStr">
+        <is>
+          <t>-38.2099256896515,178.33414912073775</t>
+        </is>
+      </c>
+      <c r="I446" t="inlineStr">
+        <is>
+          <t>-38.210630158843294,178.33410917467077</t>
+        </is>
+      </c>
+      <c r="J446" t="inlineStr">
+        <is>
+          <t>-38.211332160833194,178.33399841684079</t>
+        </is>
+      </c>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>-38.212026477921384,178.33385463773368</t>
+        </is>
+      </c>
+      <c r="L446" t="inlineStr">
+        <is>
+          <t>-38.21269445905961,178.33364321906947</t>
+        </is>
+      </c>
+      <c r="M446" t="inlineStr">
+        <is>
+          <t>-38.213364535158725,178.33343253943198</t>
+        </is>
+      </c>
+      <c r="N446" t="inlineStr">
+        <is>
+          <t>-38.21406441801143,178.33330830461435</t>
+        </is>
+      </c>
+      <c r="O446" t="inlineStr">
+        <is>
+          <t>-38.21480079190166,178.3332069579676</t>
+        </is>
+      </c>
+      <c r="P446" t="inlineStr">
+        <is>
+          <t>-38.215555641206734,178.3332095919222</t>
+        </is>
+      </c>
+      <c r="Q446" t="inlineStr">
+        <is>
+          <t>-38.21629638226756,178.33331457315455</t>
+        </is>
+      </c>
+      <c r="R446" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-16 21:53:38+00:00</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>-38.205729338912015,178.3338612829284</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>-38.20643584599614,178.33387349303882</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>-38.20713913766872,178.33394251461496</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>-38.20784451448274,178.33397449527848</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>-38.20854649605849,178.3340664703932</t>
+        </is>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>-38.209234301011826,178.33416366330047</t>
+        </is>
+      </c>
+      <c r="H447" t="inlineStr">
+        <is>
+          <t>-38.20992642576148,178.33416926274455</t>
+        </is>
+      </c>
+      <c r="I447" t="inlineStr">
+        <is>
+          <t>-38.210630973523024,178.33413102288</t>
+        </is>
+      </c>
+      <c r="J447" t="inlineStr">
+        <is>
+          <t>-38.211332869438195,178.33401742041656</t>
+        </is>
+      </c>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>-38.212027218816964,178.33386736239353</t>
+        </is>
+      </c>
+      <c r="L447" t="inlineStr">
+        <is>
+          <t>-38.212695692906095,178.33365358266565</t>
+        </is>
+      </c>
+      <c r="M447" t="inlineStr">
+        <is>
+          <t>-38.21336629634121,178.33344359481455</t>
+        </is>
+      </c>
+      <c r="N447" t="inlineStr">
+        <is>
+          <t>-38.21406310157219,178.33330004091448</t>
+        </is>
+      </c>
+      <c r="O447" t="inlineStr">
+        <is>
+          <t>-38.21480088258616,178.33319055296832</t>
+        </is>
+      </c>
+      <c r="P447" t="inlineStr">
+        <is>
+          <t>-38.21556045983199,178.33318882518898</t>
+        </is>
+      </c>
+      <c r="Q447" t="inlineStr">
+        <is>
+          <t>-38.216303274551535,178.33329071624303</t>
+        </is>
+      </c>
+      <c r="R447" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
